--- a/examples/座位表-导入参考表格.xlsx
+++ b/examples/座位表-导入参考表格.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23775" windowHeight="13875"/>
+    <workbookView windowWidth="23775" windowHeight="13875" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="网页配置" sheetId="5" r:id="rId1"/>
@@ -525,12 +525,72 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.15"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -849,7 +909,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -873,16 +933,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -891,93 +951,104 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1415,10 +1486,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
+      <c r="B1" s="13"/>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
@@ -1511,16 +1582,16 @@
       <c r="L2" t="s">
         <v>5</v>
       </c>
-      <c r="M2" t="s">
-        <v>5</v>
-      </c>
-      <c r="N2" t="s">
-        <v>5</v>
-      </c>
-      <c r="O2" t="s">
-        <v>5</v>
-      </c>
-      <c r="P2" t="s">
+      <c r="M2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="Q2" t="s">
@@ -1531,49 +1602,49 @@
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="4" t="s">
         <v>13</v>
       </c>
       <c r="I3" t="s">
         <v>14</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="O3" t="s">
+      <c r="O3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="P3" t="s">
+      <c r="P3" s="7" t="s">
         <v>21</v>
       </c>
       <c r="Q3" t="s">
@@ -1584,49 +1655,49 @@
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I4" t="s">
         <v>14</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="O4" t="s">
+      <c r="O4" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="P4" t="s">
+      <c r="P4" s="7" t="s">
         <v>35</v>
       </c>
       <c r="Q4" t="s">
@@ -1637,49 +1708,49 @@
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="8" t="s">
         <v>42</v>
       </c>
       <c r="I5" t="s">
         <v>14</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N5" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="O5" t="s">
+      <c r="O5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="P5" t="s">
+      <c r="P5" s="7" t="s">
         <v>49</v>
       </c>
       <c r="Q5" t="s">
@@ -1690,49 +1761,49 @@
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="8" t="s">
         <v>56</v>
       </c>
       <c r="I6" t="s">
         <v>14</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M6" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="N6" t="s">
+      <c r="N6" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="O6" t="s">
-        <v>5</v>
-      </c>
-      <c r="P6" t="s">
+      <c r="O6" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="P6" s="10" t="s">
         <v>62</v>
       </c>
       <c r="Q6" t="s">
@@ -1743,49 +1814,49 @@
       <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="12" t="s">
         <v>69</v>
       </c>
       <c r="I7" t="s">
         <v>14</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="M7" t="s">
+      <c r="M7" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="N7" t="s">
+      <c r="N7" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="O7" t="s">
+      <c r="O7" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="P7" t="s">
+      <c r="P7" s="10" t="s">
         <v>76</v>
       </c>
       <c r="Q7" t="s">
@@ -1796,49 +1867,49 @@
       <c r="A8" t="s">
         <v>5</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="12" t="s">
         <v>5</v>
       </c>
       <c r="I8" t="s">
         <v>14</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="M8" t="s">
+      <c r="M8" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="N8" t="s">
+      <c r="N8" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="O8" t="s">
+      <c r="O8" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="P8" t="s">
+      <c r="P8" s="10" t="s">
         <v>89</v>
       </c>
       <c r="Q8" t="s">
@@ -1907,7 +1978,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A9:Q9 C8:Q8 A8 O7:Q7 E7:M7 A7:C7 F6:Q6 A6:D6 Q5 N5:O5 E5:L5 A5:B5 A4:Q4 L3:Q3 G3:J3 A3:E3 A1:Q2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:Q2 A3:E3 G3:J3 L3:Q3 A4:Q4 A5:B5 E5:L5 N5:O5 Q5 A6:D6 F6:Q6 A7:C7 E7:M7 O7:Q7 A8 C8:Q8 A9:Q9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2591,7 +2662,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A11:B83 A9:A10 A2:B2 A3:A7 A8:B8 A1" numberStoredAsText="1"/>
+    <ignoredError sqref="A1 A8:B8 A3:A7 A2:B2 A9:A10 A11:B83" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>